--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4526,30 +4526,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>-6.900%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>19291085</t>
+          <t>-1719175</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>217747</v>
+        <v>14939</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>209542374</t>
+          <t>24801598</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4559,7 +4564,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>SFMA-134877323</t>
+          <t>SFMA-134676709</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4569,12 +4574,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134877323/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4586,78 +4591,223 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>11/20/2025</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>3.800%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-6.000%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-30891218</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>584013</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>517584852</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SFMA-134676709</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>19291085</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>217747</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>209542374</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SFMA-134877323</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134877323/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>03/21/2025</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>11.000%</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>7.900%</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>4313582</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="I53" t="n">
         <v>45254</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>54602309</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>55.000%</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-2.500%</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>TRVD-G134446033</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>FILED FOR USE</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,12 +511,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02/27/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -536,30 +536,30 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1444531</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>11400</v>
+        <v>105270</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14445306</t>
+          <t>339699416</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-14.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ALSE-134412807</t>
+          <t>ALSE-134221060</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134412807/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134221060/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -606,45 +606,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>366053</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3857</v>
+        <v>2364</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5463480</t>
+          <t>8038216</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ALSE-134468969</t>
+          <t>ALSE-134221152</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134468969/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134221152/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04/21/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -715,21 +715,21 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11400</v>
+        <v>182</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12996416</t>
+          <t>41581</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ALSE-134485149</t>
+          <t>ALSE-134221244</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134485149/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134221244/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/16/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -786,30 +786,30 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4555296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>86301</v>
+        <v>3629</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>325378305</t>
+          <t>11195039</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ALSE-134507608</t>
+          <t>ALSE-134221581</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134507608/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134221581/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -866,35 +866,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>492869</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>9260</v>
+        <v>1083</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2651506</t>
+          <t>3213723</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>40.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ALSE-134520039</t>
+          <t>ALSE-134221668</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134520039/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134221668/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -936,22 +936,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -970,21 +970,21 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>85</v>
+        <v>1227</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>124015</t>
+          <t>814411</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-9.600%</t>
+          <t>-0.300%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-134553327</t>
+          <t>ALSE-134222219</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134553327/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134222219/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08/19/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-130667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>17653</v>
+        <v>23949</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>43555674</t>
+          <t>7090928</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>-0.900%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134600254</t>
+          <t>ALSE-134223835</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134600254/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134223835/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>01/13/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1121,40 +1121,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8021887</t>
+          <t>111890</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>49469</v>
+        <v>8373</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>74970908</t>
+          <t>4300425</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18.700%</t>
+          <t>12.300%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134604458</t>
+          <t>ALSE-134353096</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134604458/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134353096/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>02/27/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1216,30 +1216,30 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-10.000%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1444531</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10281117</t>
+          <t>14445306</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.500%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134652121</t>
+          <t>ALSE-134412807</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134412807/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1276,55 +1276,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.700%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.700%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>366053</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3857</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2945067</t>
+          <t>5463480</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134652121</t>
+          <t>ALSE-134468969</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134468969/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>04/21/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5404589</t>
+          <t>12996416</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.900%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134652121</t>
+          <t>ALSE-134485149</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134485149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12/01/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1461,40 +1461,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>330809</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7642</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3341510</t>
+          <t>264560456</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>63.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-20.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134740715</t>
+          <t>ALSE-134494538</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134740715/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134494538/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1531,45 +1531,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>06/16/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.400%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.400%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4555296</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12890</v>
+        <v>86301</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1320271</t>
+          <t>325378305</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134752872</t>
+          <t>ALSE-134507608</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134752872/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134507608/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1631,35 +1631,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>265332</t>
+          <t>492869</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1374</v>
+        <v>9260</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4738080</t>
+          <t>2651506</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>9.400%</t>
+          <t>40.100%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134771605</t>
+          <t>ALSE-134520039</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134771605/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134520039/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01/26/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1716,40 +1716,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>504118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8580</v>
+        <v>85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4498444</t>
+          <t>124015</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>38.700%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.300%</t>
+          <t>-9.600%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134808921</t>
+          <t>ALSE-134553327</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134808921/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134553327/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>08/19/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1801,40 +1801,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.300%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-130667</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>13481</v>
+        <v>17653</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5778763</t>
+          <t>43555674</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>538.800%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-71.000%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GECC-134389837</t>
+          <t>ALSE-134600254</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134389837/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134600254/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1871,55 +1871,55 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.200%</t>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8021887</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>13481</v>
+        <v>49469</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5778763</t>
+          <t>74970908</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>538.800%</t>
+          <t>18.700%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-71.000%</t>
+          <t>5.300%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>GECC-134419173</t>
+          <t>ALSE-134604458</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134419173/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134604458/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>06/19/2025</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>924</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2839855</t>
+          <t>10281117</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GECC-134547737</t>
+          <t>ALSE-134652121</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>06/19/2025</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>41257</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>117600987</t>
+          <t>2945067</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>15.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-14.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GECC-134547737</t>
+          <t>ALSE-134652121</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>06/19/2025</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6801</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18068540</t>
+          <t>5404589</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GECC-134547737</t>
+          <t>ALSE-134652121</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>06/19/2025</t>
+          <t>12/01/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2226,40 +2226,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.700%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>330809</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2316</v>
+        <v>7642</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6079130</t>
+          <t>3341510</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>63.600%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-20.300%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GECC-134547737</t>
+          <t>ALSE-134740715</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134740715/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2296,27 +2296,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06/19/2025</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2330,21 +2330,21 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6098</v>
+        <v>12890</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13155062</t>
+          <t>1320271</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20.700%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-14.600%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GECC-134547737</t>
+          <t>ALSE-134752872</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134752872/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06/19/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2401,35 +2401,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>265332</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>43122</v>
+        <v>1374</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>97949596</t>
+          <t>4738080</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20.700%</t>
+          <t>9.400%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-14.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GECC-134547737</t>
+          <t>ALSE-134771605</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134771605/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2466,80 +2466,80 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03/17/2026</t>
+          <t>01/26/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>504118</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>53</v>
+        <v>8580</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>39520</t>
+          <t>4498444</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>38.700%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-20.200%</t>
+          <t>2.300%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GECC-134721778</t>
+          <t>ALSE-134808921</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134808921/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03/17/2026</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2585,46 +2585,46 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2633</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1204116</t>
+          <t>2892898</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-26.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GECC-134721778</t>
+          <t>GECC-134263694</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134263694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/17/2026</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2670,46 +2670,46 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>233327</t>
+          <t>139556665</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-21.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GECC-134721778</t>
+          <t>GECC-134263694</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134263694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03/17/2026</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2755,46 +2755,46 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>111472</t>
+          <t>19216181</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>16.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-22.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GECC-134721778</t>
+          <t>GECC-134263694</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134263694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>03/17/2026</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2840,46 +2840,46 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1416</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>835845</t>
+          <t>6473462</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-18.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GECC-134721778</t>
+          <t>GECC-134263694</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134263694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2925,11 +2925,11 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>5770311</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>GECC-134263694</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134263694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2834447</t>
+          <t>84507689</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>GECC-134263694</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134263694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3095,11 +3095,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>13794</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>35859126</t>
+          <t>5923350</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>GECC-134264301</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134264301/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.200%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>13481</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>5778763</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>538.800%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-71.000%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>GECC-134389837</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134389837/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3246,40 +3246,40 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>0.200%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>13481</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>5778763</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>538.800%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-11.400%</t>
+          <t>-71.000%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>LBPM-134597407</t>
+          <t>GECC-134419173</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134419173/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>06/19/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>-8.700%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3346,25 +3346,25 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>14257</v>
+        <v>924</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>39036258</t>
+          <t>2839855</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-79.800%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>LBPM-134597407</t>
+          <t>GECC-134547737</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>06/19/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>-12.600%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>41257</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>117600987</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.800%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.800%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>GECC-134547737</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>06/19/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.700%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>14257</v>
+        <v>6801</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>39036258</t>
+          <t>18068540</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.300%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>GECC-134547737</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>06/19/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.700%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2204</v>
+        <v>2316</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5376990</t>
+          <t>6079130</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.300%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>GECC-134547737</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>06/19/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3690,21 +3690,21 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4748</v>
+        <v>6098</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8970986</t>
+          <t>13155062</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.700%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.600%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>GECC-134547737</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>06/19/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>50202</v>
+        <v>43122</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>62444827</t>
+          <t>97949596</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.700%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.600%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>GECC-134547737</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>03/17/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3856,50 +3856,50 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-15732</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>16348</v>
+        <v>53</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>52382609</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4.100%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-22.500%</t>
+          <t>-20.200%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>LBPM-134525495</t>
+          <t>GECC-134721778</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>03/17/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3926,65 +3926,65 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>476474</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8739</v>
+        <v>2633</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4890603</t>
+          <t>1204116</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>21.900%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-26.100%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>LBPM-134654157</t>
+          <t>GECC-134721778</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3996,80 +3996,80 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/17/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>509073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4440</v>
+        <v>500</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>10181049</t>
+          <t>233327</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>20.500%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-21.000%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LBPM-134773745</t>
+          <t>GECC-134721778</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>03/17/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4096,65 +4096,65 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1132356</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>11639</v>
+        <v>236</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>37495165</t>
+          <t>111472</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>16.000%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-22.300%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>LBPM-134829691</t>
+          <t>GECC-134721778</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>03/17/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4181,7 +4181,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4195,36 +4200,46 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>14016</v>
+        <v>1416</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>23356061</t>
+          <t>835845</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>11.100%</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-18.100%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>GECC-134721778</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4236,12 +4251,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4251,7 +4266,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4265,11 +4285,21 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>462911</v>
+        <v>5</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>418122907</t>
+          <t>25473</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4279,7 +4309,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4289,12 +4319,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4306,40 +4336,55 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13949437</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>206774</v>
+        <v>672</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>176292357</t>
+          <t>2834447</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4349,7 +4394,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134384912</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4359,12 +4404,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4421,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4394,22 +4439,37 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-495049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>15062</v>
+        <v>13794</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>25658085</t>
+          <t>35859126</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4419,7 +4479,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4429,12 +4489,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4506,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4464,22 +4524,37 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-10324631</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>560065</v>
+        <v>7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>538015103</t>
+          <t>29232</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4489,7 +4564,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4499,12 +4574,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4591,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4536,25 +4611,35 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-6.900%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-1719175</t>
+          <t>881</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>14939</v>
+        <v>8</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>24801598</t>
+          <t>19326</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>13.400%</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-11.400%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4564,7 +4649,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>LBPM-134597407</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4574,12 +4659,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4676,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4611,25 +4696,35 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3.800%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-6.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-30891218</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>584013</v>
+        <v>14257</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>517584852</t>
+          <t>39036258</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>21.800%</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-79.800%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4639,7 +4734,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>LBPM-134597407</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4649,12 +4744,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4666,40 +4761,55 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>19291085</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>217747</v>
+        <v>8</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>209542374</t>
+          <t>19326</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4709,7 +4819,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>SFMA-134877323</t>
+          <t>LBPM-134677038</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4719,12 +4829,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134877323/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4736,80 +4846,2420 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>14257</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>39036258</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>LBPM-134677038</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>2204</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>5376990</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>LBPM-134677038</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>PRGS-134200135</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>PRGS-134200159</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>PRGS-134225668</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>PRGS-134225724</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Progressive Advanced Insurance Company</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-2.427%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-1.403%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-1557879</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>119266</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>111039134</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-2.355%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>PRGS-134347002</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-0.049%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-1.870%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-993</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>50</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>53076</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>-0.794%</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-1.961%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>PRGS-134347002</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Progressive Classic Insurance Company</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-0.049%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-1.870%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-598820</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>18828</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>32022437</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-2.655%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>PRGS-134347002</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-2.427%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-1.403%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-673618</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>41137</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>48012704</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-2.062%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>PRGS-134347002</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-0.049%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-1.870%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-4714</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>188</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>252084</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>-1.103%</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-2.262%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>PRGS-134347002</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Progressive Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-0.049%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-1.870%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-2314125</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>79562</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>123749982</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-2.778%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>PRGS-134347002</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-2.600%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-5.200%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-671838</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>6235</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>13008016</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>35.100%</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>LBPM-134320459</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>4748</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>8970986</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>LBPM-134386267</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>50202</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>62444827</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>LBPM-134386267</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-15732</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>16348</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>52382609</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-22.500%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>LBPM-134525495</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10/27/2025</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>9.700%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>9.700%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>476474</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>8739</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>4890603</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>21.500%</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>LBPM-134654157</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>12.500%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>509073</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>4440</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>10181049</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>LBPM-134773745</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>9.200%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1132356</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>11639</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>37495165</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>LBPM-134829691</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>14016</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>23356061</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SFMA-134294156</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>462911</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>418122907</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SFMA-134294156</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-4.300%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-1256900</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>15971</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>29076065</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>SFMA-134298166</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-1.700%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-9190766</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>548179</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>528271050</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SFMA-134298166</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>03/15/2025</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>7.900%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>13949437</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>206774</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>176292357</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SFMA-134384912</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>08/25/2025</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-495049</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>15062</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>25658085</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>SFMA-134574907</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>08/25/2025</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-10324631</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>560065</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>538015103</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>SFMA-134574907</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>11/20/2025</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-6.900%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-1719175</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>14939</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>24801598</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SFMA-134676709</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11/20/2025</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>3.800%</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-6.000%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-30891218</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>584013</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>517584852</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>SFMA-134676709</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>03/21/2025</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>11.000%</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>7.900%</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>4313582</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="I81" t="n">
         <v>45254</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>54602309</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>55.000%</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>-2.500%</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>TRVD-G134446033</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>FILED FOR USE</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-2.800%</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-2.400%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-1488305</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>45752</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>62012701</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>-5.200%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>TRVD-G134766674</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4261,17 +4261,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4285,11 +4285,11 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>LBPM-134332238</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134332238/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4346,45 +4346,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.900%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-237679</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>672</v>
+        <v>950</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2834447</t>
+          <t>4031663</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.720%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.340%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>LBPM-134332238</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134332238/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4431,45 +4431,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-6.000%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10060</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>13794</v>
+        <v>66</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35859126</t>
+          <t>167578</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.600%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-6.500%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>LBPM-134332238</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134332238/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4511,50 +4511,50 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.880%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1898586</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>14649</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>32303814</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.900%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-6.400%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>LBPM-134332238</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134332238/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4591,55 +4591,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>-5.890%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>-293212</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>3291</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>4980036</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-11.400%</t>
+          <t>-6.600%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>LBPM-134597407</t>
+          <t>LBPM-134332238</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134332238/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4676,12 +4676,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4706,25 +4706,25 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>14257</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>39036258</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-79.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>LBPM-134597407</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4761,12 +4761,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4795,11 +4795,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>672</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>2834447</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4846,12 +4846,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4880,11 +4880,11 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>14257</v>
+        <v>13794</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>39036258</t>
+          <t>35859126</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4965,11 +4965,11 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2204</v>
+        <v>7</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>5376990</t>
+          <t>29232</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5031,65 +5031,65 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>881</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.400%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.400%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>PRGS-134200135</t>
+          <t>LBPM-134597407</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5101,12 +5101,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5131,50 +5131,50 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>14257</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39036258</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.800%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-79.800%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>PRGS-134200159</t>
+          <t>LBPM-134597407</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5220,11 +5220,11 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>PRGS-134225668</t>
+          <t>LBPM-134677038</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5271,12 +5271,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5305,11 +5305,11 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>14257</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39036258</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PRGS-134225724</t>
+          <t>LBPM-134677038</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5356,12 +5356,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Progressive Advanced Insurance Company</t>
+          <t>American Economy Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5371,30 +5371,30 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-1557879</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>119266</v>
+        <v>2204</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>111039134</t>
+          <t>5376990</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-2.355%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>LBPM-134677038</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5456,65 +5456,65 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-993</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>53076</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>-0.794%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-1.961%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>PRGS-134200135</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Progressive Classic Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5541,30 +5541,30 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-598820</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>18828</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>32022437</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5574,32 +5574,32 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-2.655%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>PRGS-134200159</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5626,30 +5626,30 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-673618</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>41137</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>48012704</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-2.062%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>PRGS-134225668</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5711,40 +5711,40 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-4714</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>252084</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-1.103%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-2.262%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>PRGS-134225724</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Advanced Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5801,25 +5801,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-2314125</t>
+          <t>-1557879</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>79562</v>
+        <v>119266</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>123749982</t>
+          <t>111039134</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-2.778%</t>
+          <t>-2.355%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5866,55 +5866,55 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-5.200%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-671838</t>
+          <t>-993</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6235</v>
+        <v>50</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>13008016</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>35.100%</t>
+          <t>-0.794%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-1.961%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>LBPM-134320459</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Progressive Classic Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5966,30 +5966,30 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-598820</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4748</v>
+        <v>18828</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8970986</t>
+          <t>32022437</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.655%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6051,30 +6051,30 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-673618</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>50202</v>
+        <v>41137</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>62444827</t>
+          <t>48012704</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.062%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6121,12 +6121,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6136,40 +6136,40 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-15732</t>
+          <t>-4714</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>16348</v>
+        <v>188</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>52382609</t>
+          <t>252084</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>4.100%</t>
+          <t>-1.103%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-22.500%</t>
+          <t>-2.262%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>LBPM-134525495</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6206,12 +6206,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6221,40 +6221,40 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>476474</t>
+          <t>-2314125</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8739</v>
+        <v>79562</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>4890603</t>
+          <t>123749982</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.778%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>LBPM-134654157</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6311,30 +6311,30 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>509073</t>
+          <t>-671838</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4440</v>
+        <v>6235</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>10181049</t>
+          <t>13008016</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>35.100%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>LBPM-134773745</t>
+          <t>LBPM-134320459</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>American Economy Insurance Company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6396,30 +6396,30 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1132356</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>11639</v>
+        <v>4748</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>37495165</t>
+          <t>8970986</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>LBPM-134829691</t>
+          <t>LBPM-134386267</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6476,7 +6476,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6490,11 +6495,21 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>14016</v>
+        <v>50202</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>23356061</t>
+          <t>62444827</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6504,7 +6519,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>LBPM-134386267</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6514,12 +6529,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6531,12 +6546,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6546,7 +6561,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6556,15 +6576,25 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15732</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>462911</v>
+        <v>16348</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>418122907</t>
+          <t>52382609</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-22.500%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6574,7 +6604,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>LBPM-134525495</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6584,12 +6614,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6631,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6616,25 +6646,40 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-4.300%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-1256900</t>
+          <t>476474</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>15971</v>
+        <v>8739</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>29076065</t>
+          <t>4890603</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>21.500%</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6644,7 +6689,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>SFMA-134298166</t>
+          <t>LBPM-134654157</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6654,12 +6699,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6671,40 +6716,55 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-1.700%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-9190766</t>
+          <t>509073</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>548179</v>
+        <v>4440</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>528271050</t>
+          <t>10181049</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6714,7 +6774,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>SFMA-134298166</t>
+          <t>LBPM-134773745</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6724,12 +6784,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6741,40 +6801,55 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>13949437</t>
+          <t>1132356</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>206774</v>
+        <v>11639</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>176292357</t>
+          <t>37495165</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6784,7 +6859,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>SFMA-134384912</t>
+          <t>LBPM-134829691</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6794,12 +6869,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6886,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6826,25 +6901,25 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-495049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>15062</v>
+        <v>14016</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>25658085</t>
+          <t>23356061</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6854,7 +6929,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>SFMA-134294156</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6864,12 +6939,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6956,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6896,25 +6971,25 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-10324631</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>560065</v>
+        <v>462911</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>538015103</t>
+          <t>418122907</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6924,7 +6999,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>SFMA-134294156</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6934,12 +7009,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6951,7 +7026,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6969,27 +7044,22 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>10.700%</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-6.900%</t>
+          <t>-4.300%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-1719175</t>
+          <t>-1256900</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>14939</v>
+        <v>15971</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>24801598</t>
+          <t>29076065</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6999,7 +7069,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>SFMA-134298166</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7009,12 +7079,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7096,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7044,27 +7114,22 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>3.800%</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-6.000%</t>
+          <t>-1.700%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-30891218</t>
+          <t>-9190766</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>584013</v>
+        <v>548179</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>517584852</t>
+          <t>528271050</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7074,7 +7139,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>SFMA-134298166</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7084,12 +7149,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7166,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>03/21/2025</t>
+          <t>03/15/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7119,11 +7184,6 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>11.000%</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>7.900%</t>
@@ -7131,25 +7191,15 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4313582</t>
+          <t>13949437</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>45254</v>
+        <v>206774</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>54602309</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>55.000%</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>-2.500%</t>
+          <t>176292357</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7159,7 +7209,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>TRVD-G134446033</t>
+          <t>SFMA-134384912</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7169,12 +7219,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7186,80 +7236,540 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>08/25/2025</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-495049</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>15062</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>25658085</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>SFMA-134574907</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>08/25/2025</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-10324631</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>560065</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>538015103</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>SFMA-134574907</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>11/20/2025</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-6.900%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-1719175</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>14939</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>24801598</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SFMA-134676709</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>11/20/2025</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>3.800%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-6.000%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-30891218</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>584013</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>517584852</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>SFMA-134676709</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>03/21/2025</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>11.000%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>7.900%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>4313582</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>45254</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>54602309</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>55.000%</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>TRVD-G134446033</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>01/23/2026</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>-2.800%</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>-2.400%</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>-1488305</t>
         </is>
       </c>
-      <c r="I82" t="n">
+      <c r="I87" t="n">
         <v>45752</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>62012701</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>-5.200%</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>TRVD-G134766674</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>FILED FOR USE</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>2025-12-17</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>07/18/2025</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-6.500%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-9.900%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-814146</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>10395</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>8262946</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GNSC-134605705</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134605705/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5390,11 +5390,11 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2204</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>5376990</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>PRGS-134200135</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PRGS-134200135</t>
+          <t>PRGS-134200159</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5579,27 +5579,27 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-134200159</t>
+          <t>PRGS-134225668</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PRGS-134225668</t>
+          <t>PRGS-134225724</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Advanced Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5711,30 +5711,30 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1557879</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>119266</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111039134</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.355%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>PRGS-134225724</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Progressive Advanced Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5801,35 +5801,35 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-1557879</t>
+          <t>-993</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>119266</v>
+        <v>50</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>111039134</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.794%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-2.355%</t>
+          <t>-1.961%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Classic Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5896,25 +5896,25 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-993</t>
+          <t>-598820</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>50</v>
+        <v>18828</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>53076</t>
+          <t>32022437</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-0.794%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-1.961%</t>
+          <t>-2.655%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Progressive Classic Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5971,25 +5971,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-598820</t>
+          <t>-673618</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>18828</v>
+        <v>41137</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>32022437</t>
+          <t>48012704</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-2.655%</t>
+          <t>-2.062%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6056,35 +6056,35 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-673618</t>
+          <t>-4714</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>41137</v>
+        <v>188</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>48012704</t>
+          <t>252084</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.103%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-2.062%</t>
+          <t>-2.262%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6151,25 +6151,25 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-4714</t>
+          <t>-2314125</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>188</v>
+        <v>79562</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>252084</t>
+          <t>123749982</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>-1.103%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-2.262%</t>
+          <t>-2.778%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6206,55 +6206,55 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-2314125</t>
+          <t>-671838</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>79562</v>
+        <v>6235</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>123749982</t>
+          <t>13008016</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>35.100%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-2.778%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>LBPM-134320459</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6291,55 +6291,55 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-5.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-671838</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6235</v>
+        <v>50202</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>13008016</t>
+          <t>62444827</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>35.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>LBPM-134320459</t>
+          <t>LBPM-134386267</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6406,25 +6406,25 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15732</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4748</v>
+        <v>16348</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8970986</t>
+          <t>52382609</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.100%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-22.500%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>LBPM-134525495</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6476,35 +6476,35 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>476474</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>50202</v>
+        <v>8739</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>62444827</t>
+          <t>4890603</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.500%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>LBPM-134654157</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6546,55 +6546,55 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-15732</t>
+          <t>509073</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>16348</v>
+        <v>4440</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>52382609</t>
+          <t>10181049</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>4.100%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-22.500%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>LBPM-134525495</t>
+          <t>LBPM-134773745</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6646,35 +6646,35 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>476474</t>
+          <t>1132356</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8739</v>
+        <v>11639</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>4890603</t>
+          <t>37495165</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>LBPM-134654157</t>
+          <t>LBPM-134829691</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6716,55 +6716,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>12.500%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>509073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4440</v>
+        <v>14016</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>10181049</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>20.000%</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>-15.000%</t>
+          <t>23356061</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6774,7 +6759,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>LBPM-134773745</t>
+          <t>SFMA-134294156</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6784,12 +6769,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6786,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6816,40 +6801,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>9.200%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1132356</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>11639</v>
+        <v>462911</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>37495165</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>6.000%</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>418122907</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6859,7 +6829,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>LBPM-134829691</t>
+          <t>SFMA-134294156</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6869,12 +6839,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6856,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6901,25 +6871,25 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.300%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1256900</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>14016</v>
+        <v>15971</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>23356061</t>
+          <t>29076065</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6929,7 +6899,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>SFMA-134298166</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6939,12 +6909,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6926,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6971,25 +6941,25 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.700%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9190766</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>462911</v>
+        <v>548179</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>418122907</t>
+          <t>528271050</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6999,7 +6969,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>SFMA-134298166</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7009,12 +6979,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7026,7 +6996,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>03/15/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7036,30 +7006,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-4.300%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-1256900</t>
+          <t>13949437</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>15971</v>
+        <v>206774</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>29076065</t>
+          <t>176292357</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7069,7 +7039,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-134298166</t>
+          <t>SFMA-134384912</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7079,12 +7049,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7096,12 +7066,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7116,20 +7086,20 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-1.700%</t>
+          <t>-1.900%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-9190766</t>
+          <t>-495049</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>548179</v>
+        <v>15062</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>528271050</t>
+          <t>25658085</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7139,7 +7109,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>SFMA-134298166</t>
+          <t>SFMA-134574907</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7149,12 +7119,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7166,40 +7136,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-1.900%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>13949437</t>
+          <t>-10324631</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>206774</v>
+        <v>560065</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>176292357</t>
+          <t>538015103</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7209,7 +7179,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>SFMA-134384912</t>
+          <t>SFMA-134574907</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7219,12 +7189,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7206,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7254,22 +7224,27 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>-6.900%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-495049</t>
+          <t>-1719175</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>15062</v>
+        <v>14939</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>25658085</t>
+          <t>24801598</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7279,7 +7254,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>SFMA-134676709</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7289,12 +7264,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7281,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7324,22 +7299,27 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>3.800%</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>-6.000%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-10324631</t>
+          <t>-30891218</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>560065</v>
+        <v>584013</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>538015103</t>
+          <t>517584852</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7349,7 +7329,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>SFMA-134676709</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7359,12 +7339,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7376,45 +7356,55 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>03/21/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-6.900%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-1719175</t>
+          <t>4313582</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>14939</v>
+        <v>45254</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>24801598</t>
+          <t>54602309</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>55.000%</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7424,7 +7414,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>TRVD-G134446033</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7434,12 +7424,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7451,45 +7441,55 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3.800%</t>
+          <t>-2.800%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-6.000%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-30891218</t>
+          <t>-1488305</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>584013</v>
+        <v>45752</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>517584852</t>
+          <t>62012701</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>TRVD-G134766674</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7526,55 +7526,55 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>03/21/2025</t>
+          <t>07/18/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>-6.500%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-9.900%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4313582</t>
+          <t>-814146</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>45254</v>
+        <v>10395</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>54602309</t>
+          <t>8262946</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>55.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>TRVD-G134446033</t>
+          <t>GNSC-134605705</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7594,180 +7594,10 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
-        <is>
-          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Travelers Personal Insurance Company</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>04.0 Homeowners</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-2.800%</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-2.400%</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-1488305</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>45752</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>62012701</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-5.200%</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>TRVD-G134766674</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>FILED FOR USE</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>07/18/2025</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>MGA Insurance Company, Inc.</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>19.0 Personal Auto</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-6.500%</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-9.900%</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-814146</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>10395</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>8262946</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>10.000%</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-5.000%</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>GNSC-134605705</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>FILED FOR USE</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134605705/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4596,50 +4596,50 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.890%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-293212</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3291</v>
+        <v>5</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4980036</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-6.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>LBPM-134332238</t>
+          <t>LBPM-134385701</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134332238/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>672</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>2834447</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4795,11 +4795,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>672</v>
+        <v>13794</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2834447</t>
+          <t>35859126</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4880,11 +4880,11 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>13794</v>
+        <v>7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>35859126</t>
+          <t>29232</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4951,35 +4951,35 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>881</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.400%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.400%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>LBPM-134385701</t>
+          <t>LBPM-134597407</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5041,30 +5041,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>-319</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>14257</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>39036258</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>21.800%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-11.400%</t>
+          <t>-79.800%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-319</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>14257</v>
+        <v>8</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>39036258</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-79.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>LBPM-134597407</t>
+          <t>LBPM-134677038</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5220,11 +5220,11 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>14257</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>39036258</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5305,11 +5305,11 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>14257</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>39036258</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5324,27 +5324,27 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>PRGS-134200135</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PRGS-134200135</t>
+          <t>PRGS-134200159</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5494,27 +5494,27 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PRGS-134200159</t>
+          <t>PRGS-134225668</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-134225668</t>
+          <t>PRGS-134225724</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Advanced Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5626,30 +5626,30 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1557879</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>119266</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111039134</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.355%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PRGS-134225724</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Progressive Advanced Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5716,35 +5716,35 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-1557879</t>
+          <t>-993</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>119266</v>
+        <v>50</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>111039134</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.794%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-2.355%</t>
+          <t>-1.961%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Classic Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5811,25 +5811,25 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-993</t>
+          <t>-598820</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>18828</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>53076</t>
+          <t>32022437</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-0.794%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-1.961%</t>
+          <t>-2.655%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Progressive Classic Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5886,25 +5886,25 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-598820</t>
+          <t>-673618</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>18828</v>
+        <v>41137</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>32022437</t>
+          <t>48012704</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-2.655%</t>
+          <t>-2.062%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-673618</t>
+          <t>-4714</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>41137</v>
+        <v>188</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>48012704</t>
+          <t>252084</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.103%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-2.062%</t>
+          <t>-2.262%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6066,25 +6066,25 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-4714</t>
+          <t>-2314125</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>188</v>
+        <v>79562</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>252084</t>
+          <t>123749982</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-1.103%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-2.262%</t>
+          <t>-2.778%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6121,55 +6121,55 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-2314125</t>
+          <t>-671838</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>79562</v>
+        <v>6235</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>123749982</t>
+          <t>13008016</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>35.100%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-2.778%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>LBPM-134320459</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6206,55 +6206,55 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-5.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-671838</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6235</v>
+        <v>50202</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>13008016</t>
+          <t>62444827</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>35.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>LBPM-134320459</t>
+          <t>LBPM-134386267</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6321,25 +6321,25 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15732</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>50202</v>
+        <v>16348</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>62444827</t>
+          <t>52382609</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.100%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-22.500%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>LBPM-134525495</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6391,40 +6391,40 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-15732</t>
+          <t>476474</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>16348</v>
+        <v>8739</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>52382609</t>
+          <t>4890603</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>4.100%</t>
+          <t>21.500%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-22.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>LBPM-134525495</t>
+          <t>LBPM-134654157</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6461,55 +6461,55 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>476474</t>
+          <t>509073</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>8739</v>
+        <v>4440</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4890603</t>
+          <t>10181049</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>LBPM-134654157</t>
+          <t>LBPM-134773745</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6546,55 +6546,55 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>509073</t>
+          <t>1132356</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4440</v>
+        <v>11639</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>10181049</t>
+          <t>37495165</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>LBPM-134773745</t>
+          <t>LBPM-134829691</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6631,12 +6631,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6646,40 +6646,25 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>9.200%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1132356</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>11639</v>
+        <v>14016</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>37495165</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>6.000%</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>23356061</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6689,7 +6674,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>LBPM-134829691</t>
+          <t>SFMA-134294156</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6699,12 +6684,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6706,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6745,11 +6730,11 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>14016</v>
+        <v>462911</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>23356061</t>
+          <t>418122907</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6786,12 +6771,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6801,25 +6786,25 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.300%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1256900</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>462911</v>
+        <v>15971</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>418122907</t>
+          <t>29076065</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6829,7 +6814,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>SFMA-134298166</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6839,12 +6824,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6846,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6876,20 +6861,20 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-4.300%</t>
+          <t>-1.700%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-1256900</t>
+          <t>-9190766</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>15971</v>
+        <v>548179</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>29076065</t>
+          <t>528271050</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6926,40 +6911,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>03/15/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-1.700%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-9190766</t>
+          <t>13949437</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>548179</v>
+        <v>206774</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>528271050</t>
+          <t>176292357</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6969,7 +6954,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-134298166</t>
+          <t>SFMA-134384912</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6979,12 +6964,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6981,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7006,30 +6991,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-1.900%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>13949437</t>
+          <t>-495049</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>206774</v>
+        <v>15062</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>176292357</t>
+          <t>25658085</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7039,7 +7024,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-134384912</t>
+          <t>SFMA-134574907</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7049,12 +7034,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7056,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7091,15 +7076,15 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-495049</t>
+          <t>-10324631</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>15062</v>
+        <v>560065</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>25658085</t>
+          <t>538015103</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7136,12 +7121,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7154,22 +7139,27 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>-6.900%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-10324631</t>
+          <t>-1719175</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>560065</v>
+        <v>14939</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>538015103</t>
+          <t>24801598</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7179,7 +7169,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>SFMA-134676709</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7189,12 +7179,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7201,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7226,25 +7216,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>3.800%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-6.900%</t>
+          <t>-6.000%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-1719175</t>
+          <t>-30891218</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>14939</v>
+        <v>584013</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>24801598</t>
+          <t>517584852</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7281,45 +7271,55 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>03/21/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3.800%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-6.000%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-30891218</t>
+          <t>4313582</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>584013</v>
+        <v>45254</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>517584852</t>
+          <t>54602309</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>55.000%</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>TRVD-G134446033</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>03/21/2025</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7376,35 +7376,35 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>-2.800%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4313582</t>
+          <t>-1488305</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>45254</v>
+        <v>45752</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>54602309</t>
+          <t>62012701</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>55.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>TRVD-G134446033</t>
+          <t>TRVD-G134766674</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7441,55 +7441,55 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01/23/2026</t>
+          <t>07/18/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-2.800%</t>
+          <t>-6.500%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-2.400%</t>
+          <t>-9.900%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-1488305</t>
+          <t>-814146</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>45752</v>
+        <v>10395</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>62012701</t>
+          <t>8262946</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-5.200%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>TRVD-G134766674</t>
+          <t>GNSC-134605705</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7509,95 +7509,10 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
-        <is>
-          <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>07/18/2025</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>MGA Insurance Company, Inc.</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>19.0 Personal Auto</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-6.500%</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-9.900%</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-814146</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>10395</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>8262946</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>10.000%</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-5.000%</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>GNSC-134605705</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>FILED FOR USE</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134605705/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R143"/>
+  <dimension ref="A1:T143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,6 +607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,6 +707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -867,6 +907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -957,6 +1007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1047,6 +1107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1137,6 +1207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1224,7 +1304,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1404,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1504,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1604,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1704,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1804,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1904,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1857,6 +2007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1947,6 +2107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2037,6 +2207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2124,7 +2304,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2404,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2504,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2604,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2704,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2804,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2904,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2754,7 +3004,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2844,7 +3104,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2934,7 +3204,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3304,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3404,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3504,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3604,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3704,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3804,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3904,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3657,6 +4007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3747,6 +4107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3837,6 +4207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3927,6 +4307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4017,6 +4407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4107,6 +4507,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4197,6 +4607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4287,6 +4707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4377,6 +4807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4467,6 +4907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4552,6 +5002,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4642,6 +5102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4732,6 +5202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4812,6 +5292,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4899,7 +5389,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4989,7 +5489,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5589,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5689,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5789,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5889,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5989,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5529,7 +6089,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5619,7 +6189,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5709,7 +6289,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5799,7 +6389,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5889,7 +6489,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5979,7 +6589,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6689,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6789,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6889,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6989,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6429,7 +7089,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6519,7 +7189,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6609,7 +7289,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6702,6 +7392,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6792,6 +7492,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6882,6 +7592,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6972,6 +7692,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7062,6 +7792,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7152,6 +7892,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7242,6 +7992,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7329,7 +8089,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7419,7 +8189,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7509,7 +8289,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7599,7 +8389,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7689,7 +8489,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7779,7 +8589,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7869,7 +8689,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7959,7 +8789,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8889,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8989,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8229,7 +9089,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8319,7 +9189,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8412,6 +9292,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8502,6 +9392,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8589,7 +9489,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8682,6 +9592,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8772,6 +9692,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8862,6 +9792,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8952,6 +9892,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9042,6 +9992,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9132,6 +10092,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9222,6 +10192,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9309,7 +10289,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9399,7 +10389,17 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9489,7 +10489,17 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9579,7 +10589,17 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9669,7 +10689,17 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9759,7 +10789,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9849,7 +10889,17 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9939,7 +10989,17 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10029,7 +11089,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10119,7 +11189,17 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10212,6 +11292,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10302,6 +11392,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10392,6 +11492,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10482,6 +11592,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10572,6 +11692,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10662,6 +11792,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10749,7 +11889,17 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10839,7 +11989,17 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10929,7 +12089,17 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11019,7 +12189,17 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11109,7 +12289,17 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11199,7 +12389,17 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11282,6 +12482,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11362,6 +12572,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11437,6 +12657,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11512,6 +12742,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11587,6 +12827,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11677,6 +12927,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11767,6 +13027,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11842,6 +13112,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11917,6 +13197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12007,6 +13297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12097,6 +13397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12169,7 +13479,17 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12244,7 +13564,17 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12319,7 +13649,17 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12394,7 +13734,17 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12469,7 +13819,17 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12544,7 +13904,17 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12619,7 +13989,17 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12699,7 +14079,17 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12779,7 +14169,17 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12872,6 +14272,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12959,7 +14369,17 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13049,7 +14469,17 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T143"/>
+  <dimension ref="A1:U143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -614,9 +619,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,9 +720,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -814,9 +821,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -914,9 +922,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,9 +1023,10 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1114,9 +1124,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1214,9 +1225,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1314,9 +1326,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1414,9 +1427,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1514,9 +1528,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1614,9 +1629,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1714,9 +1730,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1814,9 +1831,10 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1914,9 +1932,10 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2014,9 +2033,10 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2114,9 +2134,10 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2214,9 +2235,10 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2314,9 +2336,10 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2414,9 +2437,10 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2514,9 +2538,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2614,9 +2639,10 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2714,9 +2740,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2804,7 +2831,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2814,7 +2841,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2936,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2914,7 +2946,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>reclassified</t>
         </is>
       </c>
     </row>
@@ -3014,9 +3051,10 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3114,9 +3152,10 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3214,9 +3253,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3314,9 +3354,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3414,9 +3455,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3514,9 +3556,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3604,7 +3647,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3614,7 +3657,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -3714,9 +3762,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3804,7 +3853,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3814,7 +3863,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -3914,9 +3968,10 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4014,9 +4069,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4114,9 +4170,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4214,9 +4271,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4314,9 +4372,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4414,9 +4473,10 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4514,9 +4574,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4614,9 +4675,10 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4714,9 +4776,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4814,9 +4877,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4914,9 +4978,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5009,9 +5074,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5109,9 +5175,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5209,9 +5276,10 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5299,9 +5367,10 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5399,9 +5468,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5499,9 +5569,10 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5599,9 +5670,10 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5699,9 +5771,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5799,9 +5872,10 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5899,9 +5973,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5999,9 +6074,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6099,9 +6175,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6199,9 +6276,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6299,9 +6377,10 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6399,9 +6478,10 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6499,9 +6579,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6599,9 +6680,10 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6699,9 +6781,10 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6799,9 +6882,10 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6899,9 +6983,10 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6999,9 +7084,10 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7099,9 +7185,10 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7199,9 +7286,10 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7299,9 +7387,10 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7399,9 +7488,10 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7499,9 +7589,10 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7599,9 +7690,10 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7699,9 +7791,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7799,9 +7892,10 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7899,9 +7993,10 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7999,9 +8094,10 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8099,9 +8195,10 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8199,9 +8296,10 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8299,9 +8397,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8399,9 +8498,10 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8499,9 +8599,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8599,9 +8700,10 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8699,9 +8801,10 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8799,9 +8902,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8889,7 +8993,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -8899,7 +9003,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -8989,7 +9098,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -8999,7 +9108,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9203,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9099,7 +9213,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -9199,9 +9318,10 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9299,9 +9419,10 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9399,9 +9520,10 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9489,7 +9611,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -9499,7 +9621,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -9599,9 +9726,10 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9699,9 +9827,10 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9799,9 +9928,10 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9899,9 +10029,10 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9999,9 +10130,10 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10099,9 +10231,10 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10199,9 +10332,10 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10299,9 +10433,10 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10399,9 +10534,10 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10499,9 +10635,10 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10599,9 +10736,10 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10689,7 +10827,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -10699,7 +10837,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -10789,7 +10932,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -10799,7 +10942,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -10889,7 +11037,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -10899,7 +11047,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -10989,7 +11142,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -10999,7 +11152,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11247,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11099,7 +11257,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11352,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11199,7 +11362,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -11299,9 +11467,10 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11399,9 +11568,10 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11499,9 +11669,10 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11599,9 +11770,10 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11699,9 +11871,10 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11799,9 +11972,10 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11899,9 +12073,10 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11999,9 +12174,10 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12099,9 +12275,10 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12189,7 +12366,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -12199,7 +12376,12 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -12299,9 +12481,10 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12389,7 +12572,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12399,7 +12582,12 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -12489,9 +12677,10 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12579,9 +12768,10 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12664,9 +12854,10 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12749,9 +12940,10 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12834,9 +13026,10 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12934,9 +13127,10 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13034,9 +13228,10 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13119,9 +13314,10 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13204,9 +13400,10 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13304,9 +13501,10 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13404,9 +13602,10 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13489,9 +13688,10 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13574,9 +13774,10 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13659,9 +13860,10 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13744,9 +13946,10 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13829,9 +14032,10 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13914,9 +14118,10 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13999,9 +14204,10 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14079,7 +14285,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -14089,7 +14295,12 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14380,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -14179,7 +14390,12 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -14279,9 +14495,10 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14379,9 +14596,10 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14479,9 +14697,10 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -2629,7 +2629,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2639,10 +2639,14 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2730,7 +2734,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2740,10 +2744,14 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3142,7 +3150,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3152,10 +3160,14 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6165,7 +6177,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6175,10 +6187,14 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6367,7 +6383,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6377,10 +6393,14 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6468,7 +6488,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6478,10 +6498,14 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6569,7 +6593,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6579,10 +6603,14 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6670,7 +6698,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -6680,10 +6708,14 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6771,7 +6803,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -6781,10 +6813,14 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6872,7 +6908,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -6882,10 +6918,14 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8589,7 +8629,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -8599,10 +8639,14 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8690,7 +8734,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -8700,10 +8744,14 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8791,7 +8839,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -8801,10 +8849,14 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8892,7 +8944,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -8902,10 +8954,14 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12164,7 +12220,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -12174,10 +12230,14 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12265,7 +12325,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -12275,10 +12335,14 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13678,7 +13742,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -13688,10 +13752,14 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13764,7 +13832,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -13774,10 +13842,14 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14108,7 +14180,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -14118,10 +14190,14 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14194,7 +14270,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -14204,10 +14280,14 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ut_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U149"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15022,12 +15022,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MGA Insurance Company, Inc.</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -15042,35 +15042,35 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>-1.000%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.000%</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>-329478</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3993</v>
+        <v>20031</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>9860562</t>
+          <t>32947783</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>14.600%</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-14.800%</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>GNSC-134231817</t>
+          <t>GECC-134934496</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -15088,14 +15088,9 @@
           <t>FILED FOR USE</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134231817/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134934496/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -15105,12 +15100,12 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
@@ -15123,98 +15118,2665 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-2.800%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-2.800%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-563016</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>10775</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>20107698</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>18.000%</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-22.000%</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GECC-134934496</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134934496/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>06/19/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-13.700%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-9.900%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-1088303</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>29571</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>10992956</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-19.600%</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>PRGS-134960830</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134960830/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>197443526</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>ALSE-134916971</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134916971/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>4.800%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>4.800%</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>167415</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>773</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>3487803</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>7.800%</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>ALSE-134973691</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134973691/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>45565</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>62622455</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>21.300%</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-33.500%</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>TRVD-G134956136</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134973966/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>07/12/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>45565</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>62622455</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>21.300%</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-33.500%</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>TRVD-G134981111</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134982778/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>3.200%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>LBPM-134982359</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134982359/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>3.200%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>84014</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>680</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2785650</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>4.560%</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>1.820%</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>LBPM-134982359</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134982359/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>3.200%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>98</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>224776</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>3.300%</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2.100%</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>LBPM-134982359</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134982359/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>07/11/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>3.200%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>717953</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>10203</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>23572153</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>3.700%</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>1.000%</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>LBPM-134982359</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134982359/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>07/19/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>4.200%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1.900%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>1709000</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>46192</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>92066000</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>6.860%</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-7.180%</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>FARM-135022539</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/135022539/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>07/19/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>4.200%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2.000%</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>498000</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>10545</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>24905000</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>10.130%</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-0.870%</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>FARM-135022539</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/135022539/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Farmers Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-1.500%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-178</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>4</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>11895</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>-0.600%</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>-4.300%</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>FAIG-134950469</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134950469/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Farmers Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2.100%</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>13441</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>164</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>640071</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>99.000%</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-21.000%</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>FAIG-134950469</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134950469/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Nationwide General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>7117</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>9828212</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>NWPP-G134965151</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134976380/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Nationwide Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>4053</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>7909900</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>NWPP-G134965151</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134976380/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Nationwide Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>3278</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>6179145</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>NWPP-G134965151</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134976380/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>American Family Insurance Company</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-18.300%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-9.400%</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-4760359</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>22602</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>50397454</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>145.500%</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-67.100%</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>AMFC-134974243</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134974243/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Farmers Group Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>4174</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>13607781</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>98.800%</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-45.900%</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>FAIG-134950572</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134950572/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-6.800%</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-0.050%</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-47000</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>46288</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>92879000</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>-10.450%</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>FARM-134915426</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134915426/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>40599819</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>USAA-134975943</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134980387/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>53253839</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>USAA-134975943</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134980387/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>70325998</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>USAA-134975943</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134980387/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>34229110</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>USAA-134975943</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134980387/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>8.600%</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2.700%</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>234360</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>9072</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>8680037</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>-20.000%</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>9.600%</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>rate_change_withdrawn</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GNSC-134945134</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>WITHDRAWN</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134945134/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>8.600%</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2.700%</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>234360</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>9072</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>8680037</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>-20.000%</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>9.600%</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GNSC-134970659</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134970659/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>09/22/2024</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>8.000%</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>3993</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>9860562</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GNSC-134231817</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134231817/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
           <t>07/18/2025</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>-6.500%</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>-9.900%</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H176" t="inlineStr">
         <is>
           <t>-814146</t>
         </is>
       </c>
-      <c r="I149" t="n">
+      <c r="I176" t="n">
         <v>10395</v>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J176" t="inlineStr">
         <is>
           <t>8262946</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="K176" t="inlineStr">
         <is>
           <t>10.000%</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t>-5.000%</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr">
+      <c r="N176" t="inlineStr">
         <is>
           <t>GNSC-134605705</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr">
+      <c r="O176" t="inlineStr">
         <is>
           <t>FILED FOR USE</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr">
+      <c r="P176" t="inlineStr">
         <is>
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="Q149" t="inlineStr">
+      <c r="Q176" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134605705/filing_summary.pdf</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="R176" t="inlineStr">
         <is>
           <t>pipeline_only</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
+      <c r="S176" t="inlineStr">
         <is>
           <t>original</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="T176" t="inlineStr">
         <is>
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
